--- a/tp_education_system/backend/app/exports/绩效工资审批表_2026年5月.xlsx
+++ b/tp_education_system/backend/app/exports/绩效工资审批表_2026年5月.xlsx
@@ -2028,12 +2028,12 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>填报时间: 2026年5月3日                    单位：人/元</t>
+          <t>填报时间: 2026年5月4日                    单位：人/元</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>填报时间: 2026年5月3日                    单位：人/元</t>
+          <t>填报时间: 2026年5月4日                    单位：人/元</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       <c r="E9" s="73" t="n"/>
       <c r="F9" s="74" t="inlineStr">
         <is>
-          <t>2026年5月3日</t>
+          <t>2026年5月4日</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       <c r="E18" s="73" t="n"/>
       <c r="F18" s="74" t="inlineStr">
         <is>
-          <t>2026年5月4日</t>
+          <t>2026年5月5日</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
       <c r="E30" s="73" t="n"/>
       <c r="F30" s="74" t="inlineStr">
         <is>
-          <t>2026年5月4日</t>
+          <t>2026年5月5日</t>
         </is>
       </c>
     </row>
